--- a/stories/arbres/TREE-JEU-003.xlsx
+++ b/stories/arbres/TREE-JEU-003.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Kenzo est sur le chemin de l'école, avec papa. Un cerceau fait un panier, au parc. Papa dit : on se passe le ballon. Puis chacun a un lancer. Vers le panier. Kenzo passe. Papa passe. Kenzo lance, tout doux. Panier. Passer. Chacun un lancer. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
+          <t>Kenzo est sur le chemin de l'école, avec papa. Un cerceau fait un panier, au parc. On se passe le ballon. Puis chacun a un lancer. Vers le panier. Kenzo passe. Papa passe. Kenzo lance, tout doux. Panier. Passer. Chacun un lancer. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo est sur le chemin de l'école, avec papa. Un cerceau fait un panier, au parc.
+papa|On se passe le ballon.
+narrateur|Puis chacun a un lancer. Vers le panier. Kenzo passe. Papa passe. Kenzo lance, tout doux. Panier. Passer. Chacun un lancer. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1489,6 +1513,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -1653,6 +1682,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo choisit rouge. Le ballon rouge. Kenzo passe. Puis un lancer vers le panier. Chacun un lancer. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1863,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On lance vers quoi ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2036,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a visé le panier. Kenzo a passé. Chacun un lancer. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2227,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2394,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend le ballon rouge. La couverture est douce. Kenzo passe, puis lance vers le panier. Chacun un lancer. Le ballon rouge revient. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2585,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2752,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chat. La lumière est claire. On secoue le sable. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Le cerceau est rangé. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2919,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3086,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chien. Des miettes dorment sur la table. On caresse le tissu. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Les mains sont tièdes. On vise le panier. On se passe le ballon. Chacun a un lancer. Papa serre Kenzo tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3253,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3420,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de la poule. Un chat miaule une fois. On tend la main. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Chacun a lancé. On vise le panier. On se passe le ballon. Chacun a un lancer. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3587,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3754,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend le seau bleu. Un grillon chante. Le seau bleu attend. Kenzo passe. Un lancer. Panier. Chacun un lancer. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3945,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3875,7 +3974,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Kenzo s'approche de le chat. Les chaussures font toc toc. On chante un petit air. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. On a dit bravo. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo range. Papa dit : c'est bien.</t>
+          <t>Kenzo s'approche de le chat. Les chaussures font toc toc. On chante un petit air. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. On a dit bravo. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo range. C'est bien.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4013,6 +4112,12 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chat. Les chaussures font toc toc. On chante un petit air. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. On a dit bravo. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4280,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4447,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chien. La couverture est douce. On compte jusqu'à trois. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Le cerceau est rangé. On vise le panier. On se passe le ballon. Chacun a un lancer. On souffle. Kenzo sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4614,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4661,6 +4781,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de la poule. Une cloche tinte au loin. On montre du doigt. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Les mains sont tièdes. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4948,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5115,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend le doudou. Une feuille tourne et tombe. Le doudou regarde. Kenzo passe. Papa lance. Panier. Chacun un lancer. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5306,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5473,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chat. Le bois sent le chaud. On range la chaise. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Chacun a lancé. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5640,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5807,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chien. Une goutte tombe, ploc. On range un objet. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. On a dit bravo. On vise le panier. On se passe le ballon. Chacun a un lancer. Papa serre Kenzo tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5974,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6141,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de la poule. Le savon sent la fleur. On se tient la main. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Le cerceau est rangé. On vise le panier. On se passe le ballon. Chacun a un lancer. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6308,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6305,6 +6475,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo choisit bleu. Le seau bleu devient un panier. Kenzo passe. Papa lance. Chacun un lancer. Passer. Panier. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6481,6 +6656,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Le ballon, d'abord on le fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -6649,6 +6829,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Passer. Panier. Chacun un lancer. Papa sourit. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6835,6 +7020,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6997,6 +7187,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend le ballon rouge. Les chaussures font toc toc. Le ballon frotte les mains. Passer. Panier. Chacun un lancer. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7183,6 +7378,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7207,7 +7407,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Kenzo s'approche de le chat. Le tissu est tout doux. On dit merci. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Les mains sont tièdes. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo range. Papa dit : c'est bien.</t>
+          <t>Kenzo s'approche de le chat. Le tissu est tout doux. On dit merci. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Les mains sont tièdes. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo range. C'est bien.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7345,6 +7545,12 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chat. Le tissu est tout doux. On dit merci. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Les mains sont tièdes. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7507,6 +7713,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7669,6 +7880,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chien. Une cuillère tinte. On souffle doucement. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Chacun a lancé. On vise le panier. On se passe le ballon. Chacun a un lancer. On souffle. Kenzo sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7831,6 +8047,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7993,6 +8214,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de la poule. Le sable est tiède. On écoute jusqu'au bout. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. On a dit bravo. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8155,6 +8381,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8317,6 +8548,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend le seau bleu. La terre est un peu humide. Kenzo pose le seau. Encore passer. Un lancer au panier. Chacun un lancer. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8503,6 +8739,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8665,6 +8906,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chat. Un rire court, tout petit. On attend son tour. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Le cerceau est rangé. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8827,6 +9073,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8989,6 +9240,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chien. Le papier froisse, chut. On sourit ensemble. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Les mains sont tièdes. On vise le panier. On se passe le ballon. Chacun a un lancer. Papa serre Kenzo tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9151,6 +9407,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9313,6 +9574,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de la poule. L'herbe chatouille le mollet. On pose les pieds par terre. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Chacun a lancé. On vise le panier. On se passe le ballon. Chacun a un lancer. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9475,6 +9741,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9637,6 +9908,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend le doudou. Les chaussures font toc toc. Kenzo câline, puis joue. Passer. Panier. Chacun un lancer. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9823,6 +10099,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9847,7 +10128,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Kenzo s'approche de le chat. Un pigeon roucoule. On parle tout bas. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. On a dit bravo. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo range. Papa dit : c'est bien.</t>
+          <t>Kenzo s'approche de le chat. Un pigeon roucoule. On parle tout bas. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. On a dit bravo. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo range. C'est bien.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -9985,6 +10266,12 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chat. Un pigeon roucoule. On parle tout bas. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. On a dit bravo. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10147,6 +10434,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10309,6 +10601,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chien. La fenêtre vibre un peu. On range les jouets. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Le cerceau est rangé. On vise le panier. On se passe le ballon. Chacun a un lancer. On souffle. Kenzo sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10471,6 +10768,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10633,6 +10935,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de la poule. Le lait est froid dans le verre. On s'assoit un moment. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Les mains sont tièdes. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10795,6 +11102,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10957,6 +11269,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo choisit vert. L'herbe est verte. Kenzo pose le doudou. Puis passer. Panier. Chacun un lancer. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11137,6 +11454,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Qui a le droit de lancer ?</t>
         </is>
       </c>
     </row>
@@ -11305,6 +11627,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a eu un lancer. Le panier a bougé un peu. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11491,6 +11818,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11515,7 +11847,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Kenzo prend le ballon rouge. Un pigeon roucoule. Papa dit : à toi. Un lancer. Panier. Passer. Chacun un lancer. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
+          <t>Kenzo prend le ballon rouge. Un pigeon roucoule. À toi. Un lancer. Panier. Passer. Chacun un lancer. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -11653,6 +11985,13 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend le ballon rouge. Un pigeon roucoule.
+papa|À toi.
+narrateur|Un lancer. Panier. Passer. Chacun un lancer. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11839,6 +12178,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12001,6 +12345,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chat. La corde du sac est rêche. On respire, un, deux. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Chacun a lancé. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12163,6 +12512,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12325,6 +12679,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chien. Le savon mousse entre les doigts. On referme le sac. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. On a dit bravo. On vise le panier. On se passe le ballon. Chacun a un lancer. Papa serre Kenzo tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12487,6 +12846,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12649,6 +13013,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de la poule. Un ruisseau chante. On essuie une miette. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Le cerceau est rangé. On vise le panier. On se passe le ballon. Chacun a un lancer. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12811,6 +13180,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12973,6 +13347,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend le seau bleu. Le banc est lisse. Le seau tinte. Panier. Passer. Chacun un lancer. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13159,6 +13538,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13183,7 +13567,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Kenzo s'approche de le chat. La laine gratte un peu. On met le doudou près. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Les mains sont tièdes. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo range. Papa dit : c'est bien.</t>
+          <t>Kenzo s'approche de le chat. La laine gratte un peu. On met le doudou près. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Les mains sont tièdes. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo range. C'est bien.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13321,6 +13705,12 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chat. La laine gratte un peu. On met le doudou près. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Les mains sont tièdes. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13483,6 +13873,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13645,6 +14040,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chien. Un pain croustille. On lace les chaussures. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Chacun a lancé. On vise le panier. On se passe le ballon. Chacun a un lancer. On souffle. Kenzo sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13807,6 +14207,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13969,6 +14374,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de la poule. Le savon glisse. On met le manteau. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. On a dit bravo. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14131,6 +14541,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14293,6 +14708,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend le doudou. Des miettes dorment sur la table. Le doudou a eu un tour d'honneur. Chacun un lancer. Panier. Passer. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14479,6 +14899,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14641,6 +15066,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chat. Une plume vole. On boit une gorgée. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Le cerceau est rangé. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14803,6 +15233,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14965,6 +15400,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chien. Le banc est lisse. On feuillette le livre. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Les mains sont tièdes. On vise le panier. On se passe le ballon. Chacun a un lancer. Papa serre Kenzo tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15127,6 +15567,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15289,6 +15734,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de la poule. Un grelot sonne. On referme le livre. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Chacun a lancé. On vise le panier. On se passe le ballon. Chacun a un lancer. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15451,6 +15901,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15469,7 +15924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15486,6 +15941,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>ch1: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-JEU-003.xlsx
+++ b/stories/arbres/TREE-JEU-003.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,11 @@
 narrateur|Puis chacun a un lancer. Vers le panier. Kenzo passe. Papa passe. Kenzo lance, tout doux. Panier. Passer. Chacun un lancer. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1520,6 +1530,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1687,6 +1698,7 @@
           <t>narrateur|Kenzo choisit rouge. Le ballon rouge. Kenzo passe. Puis un lancer vers le panier. Chacun un lancer. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1870,6 +1882,7 @@
           <t>narrateur|On lance vers quoi ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2041,6 +2054,7 @@
           <t>narrateur|Kenzo a visé le panier. Kenzo a passé. Chacun un lancer. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2232,6 +2246,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2399,6 +2414,7 @@
           <t>narrateur|Kenzo prend le ballon rouge. La couverture est douce. Kenzo passe, puis lance vers le panier. Chacun un lancer. Le ballon rouge revient. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2588,6 +2604,11 @@
       <c r="AW9" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -2757,6 +2778,7 @@
           <t>narrateur|Kenzo s'approche de le chat. La lumière est claire. On secoue le sable. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Le cerceau est rangé. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2924,6 +2946,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3091,6 +3114,11 @@
           <t>narrateur|Kenzo s'approche de le chien. Des miettes dorment sur la table. On caresse le tissu. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Les mains sont tièdes. On vise le panier. On se passe le ballon. Chacun a un lancer. Papa serre Kenzo tout doux.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3258,6 +3286,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3425,6 +3454,7 @@
           <t>narrateur|Kenzo s'approche de la poule. Un chat miaule une fois. On tend la main. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Chacun a lancé. On vise le panier. On se passe le ballon. Chacun a un lancer. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3592,6 +3622,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3759,6 +3790,7 @@
           <t>narrateur|Kenzo prend le seau bleu. Un grillon chante. Le seau bleu attend. Kenzo passe. Un lancer. Panier. Chacun un lancer. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3948,6 +3980,11 @@
       <c r="AW17" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -4118,6 +4155,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4285,6 +4323,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4452,6 +4491,11 @@
           <t>narrateur|Kenzo s'approche de le chien. La couverture est douce. On compte jusqu'à trois. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Le cerceau est rangé. On vise le panier. On se passe le ballon. Chacun a un lancer. On souffle. Kenzo sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4619,6 +4663,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4786,6 +4831,7 @@
           <t>narrateur|Kenzo s'approche de la poule. Une cloche tinte au loin. On montre du doigt. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Les mains sont tièdes. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4953,6 +4999,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5120,6 +5167,7 @@
           <t>narrateur|Kenzo prend le doudou. Une feuille tourne et tombe. Le doudou regarde. Kenzo passe. Papa lance. Panier. Chacun un lancer. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5309,6 +5357,11 @@
       <c r="AW25" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -5478,6 +5531,7 @@
           <t>narrateur|Kenzo s'approche de le chat. Le bois sent le chaud. On range la chaise. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Chacun a lancé. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5645,6 +5699,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5812,6 +5867,11 @@
           <t>narrateur|Kenzo s'approche de le chien. Une goutte tombe, ploc. On range un objet. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. On a dit bravo. On vise le panier. On se passe le ballon. Chacun a un lancer. Papa serre Kenzo tout doux.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5979,6 +6039,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6146,6 +6207,7 @@
           <t>narrateur|Kenzo s'approche de la poule. Le savon sent la fleur. On se tient la main. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Le cerceau est rangé. On vise le panier. On se passe le ballon. Chacun a un lancer. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6313,6 +6375,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6480,6 +6543,7 @@
           <t>narrateur|Kenzo choisit bleu. Le seau bleu devient un panier. Kenzo passe. Papa lance. Chacun un lancer. Passer. Panier. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6663,6 +6727,7 @@
           <t>narrateur|Le ballon, d'abord on le fait quoi ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6834,6 +6899,7 @@
           <t>narrateur|Passer. Panier. Chacun un lancer. Papa sourit. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7025,6 +7091,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7192,6 +7259,7 @@
           <t>narrateur|Kenzo prend le ballon rouge. Les chaussures font toc toc. Le ballon frotte les mains. Passer. Panier. Chacun un lancer. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7381,6 +7449,11 @@
       <c r="AW37" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -7551,6 +7624,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7718,6 +7792,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7885,6 +7960,11 @@
           <t>narrateur|Kenzo s'approche de le chien. Une cuillère tinte. On souffle doucement. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Chacun a lancé. On vise le panier. On se passe le ballon. Chacun a un lancer. On souffle. Kenzo sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8052,6 +8132,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8219,6 +8300,7 @@
           <t>narrateur|Kenzo s'approche de la poule. Le sable est tiède. On écoute jusqu'au bout. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. On a dit bravo. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8386,6 +8468,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8553,6 +8636,7 @@
           <t>narrateur|Kenzo prend le seau bleu. La terre est un peu humide. Kenzo pose le seau. Encore passer. Un lancer au panier. Chacun un lancer. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8742,6 +8826,11 @@
       <c r="AW45" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -8911,6 +9000,7 @@
           <t>narrateur|Kenzo s'approche de le chat. Un rire court, tout petit. On attend son tour. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Le cerceau est rangé. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9078,6 +9168,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9245,6 +9336,11 @@
           <t>narrateur|Kenzo s'approche de le chien. Le papier froisse, chut. On sourit ensemble. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Les mains sont tièdes. On vise le panier. On se passe le ballon. Chacun a un lancer. Papa serre Kenzo tout doux.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9412,6 +9508,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9579,6 +9676,7 @@
           <t>narrateur|Kenzo s'approche de la poule. L'herbe chatouille le mollet. On pose les pieds par terre. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Chacun a lancé. On vise le panier. On se passe le ballon. Chacun a un lancer. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9746,6 +9844,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9913,6 +10012,7 @@
           <t>narrateur|Kenzo prend le doudou. Les chaussures font toc toc. Kenzo câline, puis joue. Passer. Panier. Chacun un lancer. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10102,6 +10202,11 @@
       <c r="AW53" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -10272,6 +10377,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10439,6 +10545,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10606,6 +10713,11 @@
           <t>narrateur|Kenzo s'approche de le chien. La fenêtre vibre un peu. On range les jouets. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Le cerceau est rangé. On vise le panier. On se passe le ballon. Chacun a un lancer. On souffle. Kenzo sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10773,6 +10885,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10940,6 +11053,7 @@
           <t>narrateur|Kenzo s'approche de la poule. Le lait est froid dans le verre. On s'assoit un moment. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Les mains sont tièdes. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11107,6 +11221,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11274,6 +11389,7 @@
           <t>narrateur|Kenzo choisit vert. L'herbe est verte. Kenzo pose le doudou. Puis passer. Panier. Chacun un lancer. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11461,6 +11577,7 @@
           <t>narrateur|Qui a le droit de lancer ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11632,6 +11749,7 @@
           <t>narrateur|Kenzo a eu un lancer. Le panier a bougé un peu. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11823,6 +11941,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11992,6 +12111,7 @@
 narrateur|Un lancer. Panier. Passer. Chacun un lancer. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12181,6 +12301,11 @@
       <c r="AW65" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -12350,6 +12475,7 @@
           <t>narrateur|Kenzo s'approche de le chat. La corde du sac est rêche. On respire, un, deux. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Chacun a lancé. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12517,6 +12643,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12684,6 +12811,11 @@
           <t>narrateur|Kenzo s'approche de le chien. Le savon mousse entre les doigts. On referme le sac. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. On a dit bravo. On vise le panier. On se passe le ballon. Chacun a un lancer. Papa serre Kenzo tout doux.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12851,6 +12983,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13018,6 +13151,7 @@
           <t>narrateur|Kenzo s'approche de la poule. Un ruisseau chante. On essuie une miette. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Le cerceau est rangé. On vise le panier. On se passe le ballon. Chacun a un lancer. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13185,6 +13319,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13352,6 +13487,7 @@
           <t>narrateur|Kenzo prend le seau bleu. Le banc est lisse. Le seau tinte. Panier. Passer. Chacun un lancer. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13541,6 +13677,11 @@
       <c r="AW73" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -13711,6 +13852,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13878,6 +14020,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14045,6 +14188,11 @@
           <t>narrateur|Kenzo s'approche de le chien. Un pain croustille. On lace les chaussures. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Chacun a lancé. On vise le panier. On se passe le ballon. Chacun a un lancer. On souffle. Kenzo sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14212,6 +14360,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14379,6 +14528,7 @@
           <t>narrateur|Kenzo s'approche de la poule. Le savon glisse. On met le manteau. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. On a dit bravo. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14546,6 +14696,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14713,6 +14864,7 @@
           <t>narrateur|Kenzo prend le doudou. Des miettes dorment sur la table. Le doudou a eu un tour d'honneur. Chacun un lancer. Panier. Passer. On vise le panier. On se passe le ballon. Chacun a un lancer.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14902,6 +15054,11 @@
       <c r="AW81" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -15071,6 +15228,7 @@
           <t>narrateur|Kenzo s'approche de le chat. Une plume vole. On boit une gorgée. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Le cerceau est rangé. On vise le panier. On se passe le ballon. Chacun a un lancer. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15238,6 +15396,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15405,6 +15564,11 @@
           <t>narrateur|Kenzo s'approche de le chien. Le banc est lisse. On feuillette le livre. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Les mains sont tièdes. On vise le panier. On se passe le ballon. Chacun a un lancer. Papa serre Kenzo tout doux.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15572,6 +15736,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15739,6 +15904,7 @@
           <t>narrateur|Kenzo s'approche de la poule. Un grelot sonne. On referme le livre. On a visé le panier. On s'est passé le ballon. Chacun a eu un lancer. Chacun a lancé. On vise le panier. On se passe le ballon. Chacun a un lancer. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15906,6 +16072,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15924,7 +16091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15948,6 +16115,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15962,7 +16143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16149,6 +16330,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
